--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260514_210408.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
